--- a/opps_corrigido.xlsx
+++ b/opps_corrigido.xlsx
@@ -26756,7 +26756,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Soma_dos_Produtos</t>
+          <t>Sum_of_Products</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
